--- a/artfynd/A 33520-2025 artfynd.xlsx
+++ b/artfynd/A 33520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127738048</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33520-2025 artfynd.xlsx
+++ b/artfynd/A 33520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127738048</v>
       </c>
       <c r="B2" t="n">
-        <v>57824</v>
+        <v>57830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33520-2025 artfynd.xlsx
+++ b/artfynd/A 33520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127738048</v>
       </c>
       <c r="B2" t="n">
-        <v>57830</v>
+        <v>57831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33520-2025 artfynd.xlsx
+++ b/artfynd/A 33520-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127738048</v>
       </c>
       <c r="B2" t="n">
-        <v>57831</v>
+        <v>57843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33520-2025 artfynd.xlsx
+++ b/artfynd/A 33520-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127738048</v>
       </c>
       <c r="B2" t="n">
-        <v>57843</v>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,6 +788,131 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125024050</v>
+      </c>
+      <c r="B3" t="n">
+        <v>111128</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Valeriana dioica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Landamärket, SO, Småvänderot, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>372079</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6247956</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ängelholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hjärnarp</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>M-Äng-0219</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>30 ex spridda längs bäcke</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Längs Käglebäcken</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joachim Falck</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33520-2025 artfynd.xlsx
+++ b/artfynd/A 33520-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127738048</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,8 +922,17 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125024050</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>